--- a/imports/Australia All Amc Registrations.xlsx
+++ b/imports/Australia All Amc Registrations.xlsx
@@ -61,7 +61,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -113,7 +113,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. SALONI  MAHAJAN   </t>
+          <t xml:space="preserve"> Dr. Hrithik  Mohan -GCAUSIP/25-26/24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -132,7 +132,7 @@
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46156.0</v>
+        <v>46171.0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -148,12 +148,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. RAJENDRA KUMAR DHANU  </t>
+          <t xml:space="preserve"> Dr. SALONI  MAHAJAN  -GCAUSIP/25-26/28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2265673</t>
+          <t/>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46099.0</v>
+        <v>46156.0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -183,17 +183,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. SHARON MATHEW  </t>
+          <t xml:space="preserve"> Dr. RAJENDRA KUMAR DHANU -GCAUSIP/25-26/021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>2265673</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -202,7 +202,7 @@
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46094.0</v>
+        <v>46099.0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -218,17 +218,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anju Ann Kuriakose  </t>
+          <t xml:space="preserve"> Dr. SHARON MATHEW -GCAUSIP/25-26/29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2264229</t>
+          <t/>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t/>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -237,28 +237,28 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46064.0</v>
+        <v>46094.0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>alfiya_goocampus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>alfiya_goocampus</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ankitha Bhanu  </t>
+          <t xml:space="preserve"> Dr. Anju Ann Kuriakose -GCAUSIP/24-25/084</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2263999</t>
+          <t>2264229</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -272,28 +272,28 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46062.0</v>
+        <v>46064.0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>alfiya_goocampus</t>
+          <t>adhithya_goocampus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alfiya_goocampus</t>
+          <t>adhithya_goocampus</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohammad Sameer  </t>
+          <t xml:space="preserve"> Dr. Ankitha Bhanu -GCAUSIP/25-26/08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2263860</t>
+          <t>2263999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46055.0</v>
+        <v>46062.0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -323,12 +323,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shalini  Srinivasan   </t>
+          <t xml:space="preserve"> Dr. Mohammad Sameer -GCAUSIP/24-25/094</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>shalini20001025@gmail.com</t>
+          <t>2263860</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -342,7 +342,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46049.0</v>
+        <v>46055.0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -358,12 +358,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Satya Sri Phani Dommeti  </t>
+          <t xml:space="preserve"> Dr. Shalini  Srinivasan  -GCAUSIP/24-25/109</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2263426</t>
+          <t>shalini20001025@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -377,28 +377,28 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46044.0</v>
+        <v>46049.0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>alfiya_goocampus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>alfiya_goocampus</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sanapala Chayadevi  </t>
+          <t xml:space="preserve"> Dr. Satya Sri Phani Dommeti -GCAUSIP/24-25/103</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2262904</t>
+          <t>2263426</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -412,7 +412,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46027.0</v>
+        <v>46044.0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -428,12 +428,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohamed  Suhail  </t>
+          <t xml:space="preserve"> Dr. Sanapala Chayadevi -GCAUSIP/25-26/016</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2262557</t>
+          <t>2262904</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46011.0</v>
+        <v>46027.0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -463,12 +463,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Hamzah Shaikh  </t>
+          <t xml:space="preserve"> Dr. Mohamed  Suhail -GCAUSIP/24-25/070</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2262423</t>
+          <t>2262557</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46007.0</v>
+        <v>46011.0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -498,12 +498,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Utkarsh  Bhatt  </t>
+          <t xml:space="preserve"> Dr. Hamzah Shaikh -GCAUSIP/25-26/020</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2261948</t>
+          <t>2262423</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>45993.0</v>
+        <v>46007.0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -533,17 +533,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Madina Sudhir  Kumar   </t>
+          <t xml:space="preserve"> Dr. Utkarsh  Bhatt -GCAUSIP/24-25/043</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2262186</t>
+          <t>2261948</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$udhIr@369#</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>45992.0</v>
+        <v>45993.0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -568,17 +568,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. SRINIVAS MURTHY SEETHARAMAIAH  </t>
+          <t xml:space="preserve"> Dr. Madina Sudhir  Kumar  -GCAUSIP/25-26/015</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2173339</t>
+          <t>2262186</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>w02M01o1@1w</t>
+          <t>$udhIr@369#</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -586,10 +586,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E15" s="1" t="n">
+        <v>45992.0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -605,17 +603,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Nikhil Paul Mathew  </t>
+          <t xml:space="preserve"> Dr. SRINIVAS MURTHY SEETHARAMAIAH -GCAUSIP/25-26/01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2261850</t>
+          <t>2173339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>w02M01o1@1w</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -623,8 +621,10 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>45988.0</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Vachan MR    </t>
+          <t xml:space="preserve"> Dr. Nikhil Paul Mathew -GCAUSIP/24-25/111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2261849</t>
+          <t>2261850</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anjana Kurian  </t>
+          <t xml:space="preserve"> Dr. Vachan MR   -GCAUSIP/24-25/023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2261085</t>
+          <t>2261849</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45960.0</v>
+        <v>45988.0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -710,12 +710,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sarvesh teja Gudipudi  </t>
+          <t xml:space="preserve"> Dr. Anjana Kurian -GCAUSIP/24-25/087</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2260943</t>
+          <t>2261085</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>45954.0</v>
+        <v>45960.0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aryaa Dixit  </t>
+          <t xml:space="preserve"> Dr. Sarvesh teja Gudipudi -GCAUSIP/25-26/019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2260465</t>
+          <t>2260943</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45937.0</v>
+        <v>45954.0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -780,12 +780,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aashi Jain  </t>
+          <t xml:space="preserve"> Dr. Aryaa Dixit -GCAUSIP/25-26/018</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2260501</t>
+          <t>2260465</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Repalle  Surekha  </t>
+          <t xml:space="preserve"> Dr. Aashi Jain -GCAUSIP/24-25/012</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2260320</t>
+          <t>2260501</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45931.0</v>
+        <v>45937.0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -850,12 +850,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Kaushik K R  </t>
+          <t xml:space="preserve"> Dr. Repalle  Surekha -GCAUSIP/24-25/108</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2260298</t>
+          <t>2260320</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="E23" s="1" t="n">
-        <v>45930.0</v>
+        <v>45931.0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -885,12 +885,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Pooja Manna  </t>
+          <t xml:space="preserve"> Dr. Kaushik K R -GCAUSIP/24-25/101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2259997</t>
+          <t>2260298</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="E24" s="1" t="n">
-        <v>45919.0</v>
+        <v>45930.0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -920,12 +920,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Yenni Lavanya Kumari  </t>
+          <t xml:space="preserve"> Dr. Pooja Manna -GCAUSIP/24-25/044</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2259730</t>
+          <t>2259997</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="E25" s="1" t="n">
-        <v>45910.0</v>
+        <v>45919.0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -955,12 +955,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Indhuja Sundaram  </t>
+          <t xml:space="preserve"> Dr. Yenni Lavanya Kumari -GCAUSIP/24-25/102</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2259072</t>
+          <t>2259730</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="E26" s="1" t="n">
-        <v>45880.0</v>
+        <v>45910.0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -990,12 +990,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Hareesh Haridas  </t>
+          <t xml:space="preserve"> Dr. Indhuja Sundaram -GCAUSIP/25-26/03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2259071</t>
+          <t>2259072</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Subitha Maria Pius  </t>
+          <t xml:space="preserve"> Dr. Hareesh Haridas -GCAUSIP/24-25/105</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2259069</t>
+          <t>2259071</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1060,12 +1060,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Tarun K R Reddy  </t>
+          <t xml:space="preserve"> Dr. Subitha Maria Pius -GCAUSIP/24-25/081</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2258239</t>
+          <t>2259069</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="E29" s="1" t="n">
-        <v>45859.0</v>
+        <v>45880.0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1095,12 +1095,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Dhruv Khatkar  </t>
+          <t xml:space="preserve"> Dr. Tarun K R Reddy -GCAUSIP/24-25/095</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2258247</t>
+          <t>2258239</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1130,12 +1130,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Rahul Chopra  </t>
+          <t xml:space="preserve"> Dr. Dhruv Khatkar -GCAUSIP/24-25/069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2258240</t>
+          <t>2258247</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. NITHISH KANNAA  P G  </t>
+          <t xml:space="preserve"> Dr. Rahul Chopra -GCAUSIP/25-26/02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2257184</t>
+          <t>2258240</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1183,10 +1183,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E32" s="1" t="n">
+        <v>45859.0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1202,12 +1200,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sai Vardhan Reddy Posam  </t>
+          <t xml:space="preserve"> Dr. NITHISH KANNAA  P G -GCAUSIP/25-26/04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2257147</t>
+          <t>2257184</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1220,12 +1218,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>45828.0</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>megha_goocampus</t>
+          <t>adhithya_goocampus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sonee Bless S  </t>
+          <t xml:space="preserve"> Dr. Sai Vardhan Reddy Posam -GCAUSIP/24-25/050</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2256608</t>
+          <t>2257147</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>45814.0</v>
+        <v>45828.0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>megha_goocampus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1272,12 +1272,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Surbhi Dumra  </t>
+          <t xml:space="preserve"> Dr. Sonee Bless S -GCAUSIP/24-25/110</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2256147</t>
+          <t>2256608</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>45803.0</v>
+        <v>45814.0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1300,19 +1300,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>megha_goocampus</t>
+          <t>adhithya_goocampus</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Joel Jerusha Thathapudi  </t>
+          <t xml:space="preserve"> Dr. Surbhi Dumra -GCAUSIP/24-25/090</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2255260</t>
+          <t>2256147</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>45783.0</v>
+        <v>45803.0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1335,19 +1335,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>adhithya_goocampus</t>
+          <t>megha_goocampus</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aarti  Vishwakarma  </t>
+          <t xml:space="preserve"> Dr. Joel Jerusha Thathapudi -GCAUSIP/24-25/054</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2254740</t>
+          <t>2255260</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>45770.0</v>
+        <v>45783.0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1377,12 +1377,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Revanth Srinivas  </t>
+          <t xml:space="preserve"> Dr. Aarti  Vishwakarma -GCAUSIP/24-25/099</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2254719</t>
+          <t>2254740</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>45769.0</v>
+        <v>45770.0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Joshua Shaji Kochumman  </t>
+          <t xml:space="preserve"> Dr. Revanth Srinivas -GCAUSIP/24-25/067</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2254155</t>
+          <t>2254719</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>45755.0</v>
+        <v>45769.0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1447,12 +1447,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Nidhi Sai Sunil  </t>
+          <t xml:space="preserve"> Dr. Joshua Shaji Kochumman -GCAUSIP/23-24/059</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2254098</t>
+          <t>2254155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>45754.0</v>
+        <v>45755.0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anvitha Rose George  </t>
+          <t xml:space="preserve"> Dr. Nidhi Sai Sunil -GCAUSIP/24-25/096</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2253856</t>
+          <t>2254098</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>45748.0</v>
+        <v>45754.0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1517,12 +1517,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shreeshuktha  BS  </t>
+          <t xml:space="preserve"> Dr. Anvitha Rose George -GCAUSIP/24-25/107</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2253857</t>
+          <t>2253856</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Rhea George  </t>
+          <t xml:space="preserve"> Dr. Shreeshuktha  BS -GCAUSIP/24-25/080</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2253608</t>
+          <t>2253857</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>45741.0</v>
+        <v>45748.0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1587,12 +1587,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Nourin Siraj  </t>
+          <t xml:space="preserve"> Dr. Rhea George -GCAUSIP/24-25/059</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2253576</t>
+          <t>2253608</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>45740.0</v>
+        <v>45741.0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1622,17 +1622,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Dhruva Rameshbhai  Chauhan   </t>
+          <t xml:space="preserve"> Dr. Nourin Siraj -GCAUSIP/24-25/031</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2253494</t>
+          <t>2253576</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dhruva@1912</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>45737.0</v>
+        <v>45740.0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1657,17 +1657,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Chitalapuram Sai Kiranmayee  </t>
+          <t xml:space="preserve"> Dr. Dhruva Rameshbhai  Chauhan  -GCAUSIP/24-25/025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2253487</t>
+          <t>2253494</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Dhruva@1912</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1692,17 +1692,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sahil Kapadia  </t>
+          <t xml:space="preserve"> Dr. Chitalapuram Sai Kiranmayee -GCAUSIP/24-25/098</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2253486</t>
+          <t>2253487</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sahil1412$</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="E47" s="1" t="n">
-        <v>45736.0</v>
+        <v>45737.0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1727,17 +1727,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Merlin Kuzhikkattisserikaran Raphael  </t>
+          <t xml:space="preserve"> Dr. Sahil Kapadia -GCAUSIP/24-25/022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2253334</t>
+          <t>2253486</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Sahil1412$</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="E48" s="1" t="n">
-        <v>45730.0</v>
+        <v>45736.0</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1762,12 +1762,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Dokka Keerthana  Angeline  </t>
+          <t xml:space="preserve"> Dr. Merlin Kuzhikkattisserikaran Raphael -GCAUSIP/24-25/007</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2252861</t>
+          <t>2253334</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E49" s="1" t="n">
-        <v>45719.0</v>
+        <v>45730.0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1797,12 +1797,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Allan Joe Thomas  </t>
+          <t xml:space="preserve"> Dr. Dokka Keerthana  Angeline -GCAUSIP/24-25/024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2252789</t>
+          <t>2252861</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="E50" s="1" t="n">
-        <v>45716.0</v>
+        <v>45719.0</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1832,17 +1832,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shyama Warrier  </t>
+          <t xml:space="preserve"> Dr. Allan Joe Thomas -GCAUSIP/24-25/083</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2252549</t>
+          <t>2252789</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dreamer@1998</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="E51" s="1" t="n">
-        <v>45708.0</v>
+        <v>45716.0</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1867,17 +1867,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Keshev Kannan  Anandakumar  </t>
+          <t xml:space="preserve"> Dr. Shyama Warrier -GCAUSIP/24-25/060</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2252117</t>
+          <t>2252549</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Dreamer@1998</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="E52" s="1" t="n">
-        <v>45694.0</v>
+        <v>45708.0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1902,12 +1902,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shwetha Mohan  </t>
+          <t xml:space="preserve"> Dr. Keshev Kannan  Anandakumar -GCAUSIP/24-25/066</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2252111</t>
+          <t>2252117</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aswin R J  </t>
+          <t xml:space="preserve"> Dr. Shwetha Mohan -GCAUSIP/24-25/068</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2251932</t>
+          <t>2252111</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="E54" s="1" t="n">
-        <v>45688.0</v>
+        <v>45694.0</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1972,12 +1972,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ananya Siyann Anil  </t>
+          <t xml:space="preserve"> Dr. Aswin R J -GCAUSIP/24-25/086</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2251785</t>
+          <t>2251932</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E55" s="1" t="n">
-        <v>45684.0</v>
+        <v>45688.0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2007,12 +2007,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Akshaya Akhilesh  </t>
+          <t xml:space="preserve"> Dr. Ananya Siyann Anil -GCAUSIP/24-25/075</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2251676</t>
+          <t>2251785</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>45680.0</v>
+        <v>45684.0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2042,12 +2042,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sarthak Panda  </t>
+          <t xml:space="preserve"> Dr. Akshaya Akhilesh -GCAUSIP/24-25/017</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2251368</t>
+          <t>2251676</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="E57" s="1" t="n">
-        <v>45670.0</v>
+        <v>45680.0</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2077,12 +2077,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Prajith B  </t>
+          <t xml:space="preserve"> Dr. Sarthak Panda -GCAUSIP/24-25/009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2250932</t>
+          <t>2251368</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E58" s="1" t="n">
-        <v>45652.0</v>
+        <v>45670.0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2112,12 +2112,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aysha Siddique  </t>
+          <t xml:space="preserve"> Dr. Prajith B -GCAUSIP/24-25/061</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2250723</t>
+          <t>2250932</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E59" s="1" t="n">
-        <v>45642.0</v>
+        <v>45652.0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2147,12 +2147,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Niranjana Santhosh  </t>
+          <t xml:space="preserve"> Dr. Aysha Siddique -GCAUSIP/24-25/062</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2250722</t>
+          <t>2250723</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2182,17 +2182,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shruthi Siddi  </t>
+          <t xml:space="preserve"> Dr. Niranjana Santhosh -GCAUSIP/24-25/053</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2252580</t>
+          <t>2250722</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jasn0206</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E61" s="1" t="n">
-        <v>45709.0</v>
+        <v>45642.0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2217,17 +2217,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Abishek  Thiyagarajan  </t>
+          <t xml:space="preserve"> Dr. Shruthi Siddi -GCAUSIP/24-25/076</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2250595</t>
+          <t>2252580</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Goocampus2123</t>
+          <t>jasn0206</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="E62" s="1" t="n">
-        <v>45638.0</v>
+        <v>45709.0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2252,17 +2252,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Lakshmi Narayanan  T  </t>
+          <t xml:space="preserve"> Dr. Abishek  Thiyagarajan -GCAUSIP/24-25/065</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2250604</t>
+          <t>2250595</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Goocampus2123</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Athira K S  </t>
+          <t xml:space="preserve"> Dr. Lakshmi Narayanan  T -GCAUSIP/24-25/046</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2250467</t>
+          <t>2250604</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="E64" s="1" t="n">
-        <v>45632.0</v>
+        <v>45638.0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2322,12 +2322,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Faisal Firoz  Khan  </t>
+          <t xml:space="preserve"> Dr. Athira K S -GCAUSIP/24-25/056</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2250157</t>
+          <t>2250467</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>45621.0</v>
+        <v>45632.0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2357,12 +2357,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Thusha Thulasidharan Sheeba  </t>
+          <t xml:space="preserve"> Dr. Faisal Firoz  Khan -GCAUSIP/24-25/042</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2250090</t>
+          <t>2250157</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="E66" s="1" t="n">
-        <v>45618.0</v>
+        <v>45621.0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2392,12 +2392,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Trisha  Gaur  </t>
+          <t xml:space="preserve"> Dr. Thusha Thulasidharan Sheeba -GCAUSIP/24-25/088</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2249817</t>
+          <t>2250090</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>45609.0</v>
+        <v>45618.0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2427,12 +2427,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ahmed Adam  </t>
+          <t xml:space="preserve"> Dr. Trisha  Gaur -GCAUSIP/24-25/071</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2249746</t>
+          <t>2249817</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>45607.0</v>
+        <v>45609.0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2462,17 +2462,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Rishabh Gupta  </t>
+          <t xml:space="preserve"> Dr. Ahmed Adam -GCAUSIP/24-25/041</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2249363</t>
+          <t>2249746</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goocampus@123 </t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>45593.0</v>
+        <v>45607.0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2497,17 +2497,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ramanika Latha sashi  </t>
+          <t xml:space="preserve"> Dr. Rishabh Gupta -GCAUSIP/24-25/030</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2248958</t>
+          <t>2249363</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t xml:space="preserve">Goocampus@123 </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>45580.0</v>
+        <v>45593.0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2532,12 +2532,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Siddhesh Kapadia  </t>
+          <t xml:space="preserve"> Dr. Ramanika Latha sashi -GCAUSIP/24-25/052</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2248747</t>
+          <t>2248958</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>45573.0</v>
+        <v>45580.0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2567,12 +2567,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Yuvashree Krishnamurthy  </t>
+          <t xml:space="preserve"> Dr. Siddhesh Kapadia -GCAUSIP/24-25/078</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2248867</t>
+          <t>2248747</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2602,12 +2602,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Raineera Barreto  </t>
+          <t xml:space="preserve"> Dr. Yuvashree Krishnamurthy -GCAUSIP/24-25/079</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2248751</t>
+          <t>2248867</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Venkata Goutham Chowdary Bollineni  </t>
+          <t xml:space="preserve"> Dr. Raineera Barreto -GCAUSIP/24-25/018</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2248644</t>
+          <t>2248751</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>45569.0</v>
+        <v>45573.0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2672,12 +2672,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Arnavv Bansal  </t>
+          <t xml:space="preserve"> Dr. Venkata Goutham Chowdary Bollineni -GCAUSIP/24-25/035</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2248550</t>
+          <t>2248644</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>45566.0</v>
+        <v>45569.0</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2707,12 +2707,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Tulasiram Karadhi  </t>
+          <t xml:space="preserve"> Dr. Arnavv Bansal -GCAUSIP/24-25/028</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2248320</t>
+          <t>2248550</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>45559.0</v>
+        <v>45566.0</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2742,12 +2742,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shiva Teja Akoju  </t>
+          <t xml:space="preserve"> Dr. Tulasiram Karadhi -GCAUSIP/24-25/037</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2248306</t>
+          <t>2248320</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Santhosh kumar Gajjala  </t>
+          <t xml:space="preserve"> Dr. Shiva Teja Akoju -GCAUSIP/24-25/039</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2247989</t>
+          <t>2248306</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="E78" s="1" t="n">
-        <v>45547.0</v>
+        <v>45559.0</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2812,12 +2812,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Abishek Ganesh  Ganesan  </t>
+          <t xml:space="preserve"> Dr. Santhosh kumar Gajjala -GCAUSIP/24-25/036</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2247845</t>
+          <t>2247989</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E79" s="1" t="n">
-        <v>45544.0</v>
+        <v>45547.0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anwadevi  Arun  </t>
+          <t xml:space="preserve"> Dr. Abishek Ganesh  Ganesan -GCAUSIP/24-25/038</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2247853</t>
+          <t>2247845</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sangavi Panneerselvam   </t>
+          <t xml:space="preserve"> Dr. Anwadevi  Arun -GCAUSIP/24-25/040</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2247799</t>
+          <t>2247853</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E81" s="1" t="n">
-        <v>45541.0</v>
+        <v>45544.0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2917,12 +2917,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sheeja Rayan  </t>
+          <t xml:space="preserve"> Dr. Sangavi Panneerselvam  -GCAUSIP/24-25/073</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2247736</t>
+          <t>2247799</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="E82" s="1" t="n">
-        <v>45539.0</v>
+        <v>45541.0</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2952,12 +2952,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aravind K  </t>
+          <t xml:space="preserve"> Dr. Sheeja Rayan -GCAUSIP/24-25/010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2247698</t>
+          <t>2247736</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="E83" s="1" t="n">
-        <v>45537.0</v>
+        <v>45539.0</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2987,12 +2987,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Carolyn Doris DSA  </t>
+          <t xml:space="preserve"> Dr. Aravind K -GCAUSIP/2023/050</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2247545</t>
+          <t>2247698</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="E84" s="1" t="n">
-        <v>45532.0</v>
+        <v>45537.0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3022,12 +3022,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Narmada Lanka  </t>
+          <t xml:space="preserve"> Dr. Carolyn Doris DSA -GCAUSIP/24-25/034</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2247207</t>
+          <t>2247545</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="E85" s="1" t="n">
-        <v>45520.0</v>
+        <v>45532.0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3057,12 +3057,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aju Varghese  </t>
+          <t xml:space="preserve"> Dr. Narmada Lanka -GCAUSIP/23-24/068</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2247144</t>
+          <t>2247207</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E86" s="1" t="n">
-        <v>45518.0</v>
+        <v>45520.0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3092,12 +3092,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anjaly Joy  </t>
+          <t xml:space="preserve"> Dr. Aju Varghese -GCAUSIP/2023/034</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2247124</t>
+          <t>2247144</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="E87" s="1" t="n">
-        <v>45517.0</v>
+        <v>45518.0</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3127,12 +3127,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Avelyn Thazhuthadath Kishore  </t>
+          <t xml:space="preserve"> Dr. Anjaly Joy -GCAUSIP/2023/021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2247128</t>
+          <t>2247124</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3162,12 +3162,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Dikshita Karunanidhi  </t>
+          <t xml:space="preserve"> Dr. Avelyn Thazhuthadath Kishore -GCAUSIP/2023/033</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2246605</t>
+          <t>2247128</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="E89" s="1" t="n">
-        <v>45502.0</v>
+        <v>45517.0</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3197,12 +3197,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Alna Xavier  </t>
+          <t xml:space="preserve"> Dr. Dikshita Karunanidhi -GCAUSIP/23-24/072</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2246638</t>
+          <t>2246605</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3232,12 +3232,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Kevin Mathew  </t>
+          <t xml:space="preserve"> Dr. Alna Xavier -GCAUSIP/24-25/026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2246482</t>
+          <t>2246638</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="E91" s="1" t="n">
-        <v>45498.0</v>
+        <v>45502.0</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3267,12 +3267,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Simran B  </t>
+          <t xml:space="preserve"> Dr. Kevin Mathew -GCAUSIP/2023/048</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2246487</t>
+          <t>2246482</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3302,12 +3302,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Felix Joseph  </t>
+          <t xml:space="preserve"> Dr. Simran B -GCAUSIP/24-25/002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2246491</t>
+          <t>2246487</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Bendangjungla  Pongen  </t>
+          <t xml:space="preserve"> Dr. Felix Joseph -GCAUSIP/24-25/004</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2246406</t>
+          <t>2246491</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="E94" s="1" t="n">
-        <v>45496.0</v>
+        <v>45498.0</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3372,12 +3372,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Neeraja Surendran Jolly  </t>
+          <t xml:space="preserve"> Dr. Bendangjungla  Pongen -GCAUSIP/24-25/029</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2246399</t>
+          <t>2246406</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3407,17 +3407,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Kiruba Graceline  </t>
+          <t xml:space="preserve"> Dr. Neeraja Surendran Jolly -GCAUSIP/24-25/006</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2246354</t>
+          <t>2246399</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jesus@1996</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>45495.0</v>
+        <v>45496.0</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3442,17 +3442,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Kalva Sharath Chander Reddy  </t>
+          <t xml:space="preserve"> Dr. Kiruba Graceline -GCAUSIP/24-25/003</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2245854</t>
+          <t>2246354</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ronaldo@cr7</t>
+          <t>Jesus@1996</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E97" s="1" t="n">
-        <v>45477.0</v>
+        <v>45495.0</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3477,17 +3477,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Rukksana  Karim  </t>
+          <t xml:space="preserve"> Dr. Kalva Sharath Chander Reddy -GCAUSIP/24-25/016</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2245818</t>
+          <t>2245854</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sona@12345</t>
+          <t>Ronaldo@cr7</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="E98" s="1" t="n">
-        <v>45476.0</v>
+        <v>45477.0</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3512,17 +3512,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Hussain    </t>
+          <t xml:space="preserve"> Dr. Rukksana  Karim -GCAUSIP/24-25/020</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2245645</t>
+          <t>2245818</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Sona@12345</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E99" s="1" t="n">
-        <v>45471.0</v>
+        <v>45476.0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3547,12 +3547,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Akash Babu  </t>
+          <t xml:space="preserve"> Dr. Hussain   -GCAUSIP/23-24/056</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2245570</t>
+          <t>2245645</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="E100" s="1" t="n">
-        <v>45469.0</v>
+        <v>45471.0</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Manasa K  </t>
+          <t xml:space="preserve"> Dr. Akash Babu -GCAUSIP/23-24/066</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2245564</t>
+          <t>2245570</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3617,12 +3617,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Monika Rao  </t>
+          <t xml:space="preserve"> Dr. Manasa K -GCAUSIP/24-25/005</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2245527</t>
+          <t>2245564</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="E102" s="1" t="n">
-        <v>45468.0</v>
+        <v>45469.0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3652,17 +3652,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Sai Geetha  Lakshmi Narayanan  </t>
+          <t xml:space="preserve"> Dr. Monika Rao -GCAUSIP/24-25/011</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2245227</t>
+          <t>2245527</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tn11f8106</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3670,10 +3670,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E103" s="1" t="n">
+        <v>45468.0</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3689,17 +3687,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Aayushi Nagpal  </t>
+          <t xml:space="preserve"> Dr. Sai Geetha  Lakshmi Narayanan -GCAUSIP/23-24/070</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2245082</t>
+          <t>2245227</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Tn11f8106</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3707,8 +3705,10 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E104" s="1" t="n">
-        <v>45453.0</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3724,12 +3724,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Harish Kumar P  </t>
+          <t xml:space="preserve"> Dr. Aayushi Nagpal -GCAUSIP/2023/09</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2245817</t>
+          <t>2245082</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="E105" s="1" t="n">
-        <v>45440.0</v>
+        <v>45453.0</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3759,12 +3759,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Kavya Ankireddy  </t>
+          <t xml:space="preserve"> Dr. Harish Kumar P -GCAUSIP/2023/036</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2244484</t>
+          <t>2245817</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="E106" s="1" t="n">
-        <v>45435.0</v>
+        <v>45440.0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3794,17 +3794,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Abishek Balaji  </t>
+          <t xml:space="preserve"> Dr. Kavya Ankireddy -GCAUSIP/23-24/067</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2244438</t>
+          <t>2244484</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7397024467</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="E107" s="1" t="n">
-        <v>45434.0</v>
+        <v>45435.0</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3829,17 +3829,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Lohitha Inturi  </t>
+          <t xml:space="preserve"> Dr. Abishek Balaji -GCAUSIP/23-24/063</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2243512</t>
+          <t>2244438</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>7397024467</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E108" s="1" t="n">
-        <v>45412.0</v>
+        <v>45434.0</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3864,12 +3864,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Akash Subramanian  </t>
+          <t xml:space="preserve"> Dr. Lohitha Inturi -GCAUSIP/23-24/060</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2243194</t>
+          <t>2243512</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="E109" s="1" t="n">
-        <v>45404.0</v>
+        <v>45412.0</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3899,17 +3899,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Prabhakar Rao Karanam  </t>
+          <t xml:space="preserve"> Dr. Akash Subramanian -GCAUSIP/2023/054</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2243143</t>
+          <t>2243194</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prabha@1998</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="E110" s="1" t="n">
-        <v>45401.0</v>
+        <v>45404.0</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3934,17 +3934,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anirudh Mantre  </t>
+          <t xml:space="preserve"> Dr. Prabhakar Rao Karanam -GCAUSIP/2023/049</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2243099</t>
+          <t>2243143</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Prabha@1998</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E111" s="1" t="n">
-        <v>45399.0</v>
+        <v>45401.0</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3969,12 +3969,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Prajwal Chandan  </t>
+          <t xml:space="preserve"> Dr. Anirudh Mantre -GCAUSIP/2023/040</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2243001</t>
+          <t>2243099</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="E112" s="1" t="n">
-        <v>45397.0</v>
+        <v>45399.0</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4004,12 +4004,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ganesh Prasad Y  </t>
+          <t xml:space="preserve"> Dr. Prajwal Chandan -GCAUSIP/2023/017</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2243056</t>
+          <t>2243001</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="E113" s="1" t="n">
-        <v>45398.0</v>
+        <v>45397.0</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4039,12 +4039,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Fidvi Fazal  </t>
+          <t xml:space="preserve"> Dr. Ganesh Prasad Y -GCAUSIP/23-24/057</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2242911</t>
+          <t>2243056</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="E114" s="1" t="n">
-        <v>45393.0</v>
+        <v>45398.0</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4074,12 +4074,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. David Joshua  </t>
+          <t xml:space="preserve"> Dr. Fidvi Fazal -GCAUSIP/23-24/069</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2242715</t>
+          <t>2242911</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="E115" s="1" t="n">
-        <v>45387.0</v>
+        <v>45393.0</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohan Koshy Varghese  </t>
+          <t xml:space="preserve"> Dr. David Joshua -GCAUSIP/23-24/064</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2242649</t>
+          <t>2242715</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="E116" s="1" t="n">
-        <v>45385.0</v>
+        <v>45387.0</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4144,12 +4144,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Bavleen    </t>
+          <t xml:space="preserve"> Dr. Mohan Koshy Varghese -GCAUSIP/23-24/071</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2242483</t>
+          <t>2242649</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="E117" s="1" t="n">
-        <v>45379.0</v>
+        <v>45385.0</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4179,12 +4179,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Bhargavi N  </t>
+          <t xml:space="preserve"> Dr. Bavleen   -GCAUSIP/23-24/061</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2242476</t>
+          <t>2242483</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4214,12 +4214,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Philomina Greeshma  </t>
+          <t xml:space="preserve"> Dr. Bhargavi N -GCAUSIP/2023/055</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2242354</t>
+          <t>2242476</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="E119" s="1" t="n">
-        <v>45376.0</v>
+        <v>45379.0</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4249,12 +4249,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Archa  A Pillai  </t>
+          <t xml:space="preserve"> Dr. Philomina Greeshma -GCAUSIP/2023/025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2242279</t>
+          <t>2242354</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="E120" s="1" t="n">
-        <v>45372.0</v>
+        <v>45376.0</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -4284,12 +4284,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohamed Anas  </t>
+          <t xml:space="preserve"> Dr. Archa  A Pillai -GCAUSIP/23-24/058</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2242239</t>
+          <t>2242279</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="E121" s="1" t="n">
-        <v>45371.0</v>
+        <v>45372.0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4319,12 +4319,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Parth Kansara  </t>
+          <t xml:space="preserve"> Dr. Mohamed Anas -GCAUSIP/2023/046</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2241972</t>
+          <t>2242239</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="E122" s="1" t="n">
-        <v>45363.0</v>
+        <v>45371.0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -4354,12 +4354,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohammad Nihal  </t>
+          <t xml:space="preserve"> Dr. Parth Kansara -GCAUSIP/2023/031</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2241851</t>
+          <t>2241972</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="E123" s="1" t="n">
-        <v>45359.0</v>
+        <v>45363.0</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4389,12 +4389,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Subhiksha Nirmala Muniappan  </t>
+          <t xml:space="preserve"> Dr. Mohammad Nihal -GCAUSIP/2023/042</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2241533</t>
+          <t>2241851</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="E124" s="1" t="n">
-        <v>45350.0</v>
+        <v>45359.0</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4424,17 +4424,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Keshav Singh Jaswal  </t>
+          <t xml:space="preserve"> Dr. Subhiksha Nirmala Muniappan -GCAUSIP/2023/053</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2241507</t>
+          <t>2241533</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ilikebubbles1234</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="E125" s="1" t="n">
-        <v>45349.0</v>
+        <v>45350.0</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -4459,17 +4459,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Arya Ashok  </t>
+          <t xml:space="preserve"> Dr. Keshav Singh Jaswal -GCAUSIP/23-24/062</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2241201</t>
+          <t>2241507</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Ilikebubbles1234</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="E126" s="1" t="n">
-        <v>45338.0</v>
+        <v>45349.0</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4494,12 +4494,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Angel Mariya Sebastian  </t>
+          <t xml:space="preserve"> Dr. Arya Ashok -GCAUSIP/2023/047</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2241169</t>
+          <t>2241201</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="E127" s="1" t="n">
-        <v>45337.0</v>
+        <v>45338.0</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Amrtha pradeep  </t>
+          <t xml:space="preserve"> Dr. Angel Mariya Sebastian -GCAUSIP/2023/052</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2241130</t>
+          <t>2241169</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="E128" s="1" t="n">
-        <v>45336.0</v>
+        <v>45337.0</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -4564,12 +4564,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Karthick Balasubramanian  </t>
+          <t xml:space="preserve"> Dr. Amrtha pradeep -GCAUSIP/2023/045</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2241101</t>
+          <t>2241130</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="E129" s="1" t="n">
-        <v>45335.0</v>
+        <v>45336.0</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -4599,12 +4599,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mohammad  Shibil   </t>
+          <t xml:space="preserve"> Dr. Karthick Balasubramanian -GCAUSIP/2023/023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2241072</t>
+          <t>2241101</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="E130" s="1" t="n">
-        <v>45334.0</v>
+        <v>45335.0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4634,12 +4634,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. George  James  </t>
+          <t xml:space="preserve"> Dr. Mohammad  Shibil  -GCAUSIP/2023/044</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2240917</t>
+          <t>2241072</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E131" s="1" t="n">
-        <v>45329.0</v>
+        <v>45334.0</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4669,12 +4669,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Neha Reddy Gangidi  </t>
+          <t xml:space="preserve"> Dr. George  James -GCAUSIP/2023/051</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2240888</t>
+          <t>2240917</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="E132" s="1" t="n">
-        <v>45328.0</v>
+        <v>45329.0</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anmol Singh  </t>
+          <t xml:space="preserve"> Dr. Neha Reddy Gangidi -GCAUSIP/2023/030</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2240123</t>
+          <t>2240888</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Goocampus@123G</t>
+          <t>Goocampus@123</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="E133" s="1" t="n">
-        <v>45294.0</v>
+        <v>45328.0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4739,12 +4739,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shivang Pathak  </t>
+          <t xml:space="preserve"> Dr. Anmol Singh -GCAUSIP/2023/029</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2240104</t>
+          <t>2240123</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="E134" s="1" t="n">
-        <v>45282.0</v>
+        <v>45294.0</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4774,17 +4774,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Gogula Krishna N M  </t>
+          <t xml:space="preserve"> Dr. Shivang Pathak -GCAUSIP/2023/027</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2240129</t>
+          <t>2240104</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>i_Gogula07</t>
+          <t>Goocampus@123G</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4792,10 +4792,8 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E135" s="1" t="n">
+        <v>45282.0</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4811,17 +4809,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Anamika Ray  </t>
+          <t xml:space="preserve"> Dr. Gogula Krishna N M -GCAUSIP/2023/039</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2239179</t>
+          <t>2240129</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Goocampus@123G</t>
+          <t>i_Gogula07</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4848,12 +4846,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Yashika Bopaiah  </t>
+          <t xml:space="preserve"> Dr. Anamika Ray -GCAUSIP/2023/022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2240090</t>
+          <t>2239179</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4885,12 +4883,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Ayitabathula Dilip Sai   </t>
+          <t xml:space="preserve"> Dr. Yashika Bopaiah -GCAUSIP/2023/026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2240104</t>
+          <t>2240090</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4922,17 +4920,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Lekshmi S Nair  </t>
+          <t xml:space="preserve"> Dr. Ayitabathula Dilip Sai  -GCAUSIP/2023/024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2240056</t>
+          <t>2240104</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lekshmi30@</t>
+          <t>Goocampus@123G</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4959,17 +4957,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Harini Kona  </t>
+          <t xml:space="preserve"> Dr. Lekshmi S Nair -GCAUSIP/2023/041</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2238737</t>
+          <t>2240056</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Goocampus@123G</t>
+          <t>Lekshmi30@</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4996,12 +4994,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Paul Milan  </t>
+          <t xml:space="preserve"> Dr. Harini Kona -GCAUSIP/2023/014</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2238874</t>
+          <t>2238737</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5033,12 +5031,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Asha Jeffin saleem  </t>
+          <t xml:space="preserve"> Dr. Paul Milan -GCAUSIP/2023/012</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2238547</t>
+          <t>2238874</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5070,12 +5068,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Nagabhyru Sujitha  </t>
+          <t xml:space="preserve"> Dr. Asha Jeffin saleem -GCAUSIP/2023/037</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2238176</t>
+          <t>2238547</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5107,17 +5105,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Nimish  Sunny  </t>
+          <t xml:space="preserve"> Dr. Nagabhyru Sujitha -GCAUSIP/2023/019</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2233591</t>
+          <t>2238176</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Nimish1305@</t>
+          <t>Goocampus@123G</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5144,17 +5142,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. GUNJALA ROHITH  KUMAR   </t>
+          <t xml:space="preserve"> Dr. Nimish  Sunny -GCAUSIP/2023/01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2235773</t>
+          <t>2233591</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Goocampus@123G</t>
+          <t>Nimish1305@</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5181,12 +5179,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Mahira  Sahar  </t>
+          <t xml:space="preserve"> Dr. GUNJALA ROHITH  KUMAR  -GCAUSIP/2023/05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2235347</t>
+          <t>2235773</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5218,12 +5216,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Shivam Singh Mukherjee  </t>
+          <t xml:space="preserve"> Dr. Mahira  Sahar -GCAUSIP/2023/04</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2235252</t>
+          <t>2235347</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5255,12 +5253,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Somya Bajaj  </t>
+          <t xml:space="preserve"> Dr. Shivam Singh Mukherjee -GCAUSIP/2023/018</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2235256</t>
+          <t>2235252</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5292,12 +5290,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Vishnu Besta  </t>
+          <t xml:space="preserve"> Dr. Somya Bajaj -GCAUSIP/2023/08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2234972</t>
+          <t>2235256</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5329,17 +5327,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Stuti Singla  </t>
+          <t xml:space="preserve"> Dr. Vishnu Besta -GCAUSIP/2023/06</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2234940</t>
+          <t>2234972</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Stutisingla@210</t>
+          <t>Goocampus@123G</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5366,17 +5364,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Jasmine Kaur  </t>
+          <t xml:space="preserve"> Dr. Stuti Singla -GCAUSIP/2023/015</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2234888</t>
+          <t>2234940</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Goocampus@3095</t>
+          <t>Stutisingla@210</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5403,17 +5401,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. Liz Catherine  </t>
+          <t xml:space="preserve"> Dr. Jasmine Kaur -GCAUSIP/2023/010</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2234731</t>
+          <t>2234888</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Goocampus@123</t>
+          <t>Goocampus@3095</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5440,35 +5438,72 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dr. JAYAKRISHNAN    </t>
+          <t xml:space="preserve"> Dr. Liz Catherine -GCAUSIP/2023/07</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
+          <t>2234731</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Goocampus@123</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>adhithya_goocampus</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>adhithya_goocampus</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dr. JAYAKRISHNAN   -GCAUSIP/2023/013</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>2234716</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Goocampus@123</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Goocampus@123</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>adhithya_goocampus</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>adhithya_goocampus</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>adhithya_goocampus</t>
         </is>
